--- a/summary_stats/chuuchuu_summary_2025_07.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_07.xlsx
@@ -901,16 +901,16 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O6" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R6" t="n">
         <v>56</v>
@@ -1296,25 +1296,25 @@
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>3</v>
@@ -1375,25 +1375,25 @@
         <v>125</v>
       </c>
       <c r="N12" t="n">
-        <v>1169</v>
+        <v>1129</v>
       </c>
       <c r="O12" t="n">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="P12" t="n">
-        <v>943</v>
+        <v>907</v>
       </c>
       <c r="Q12" t="n">
-        <v>739</v>
+        <v>705</v>
       </c>
       <c r="R12" t="n">
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="S12" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="T12" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="U12" t="n">
         <v>1916</v>
@@ -1612,25 +1612,25 @@
         <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="O15" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P15" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="Q15" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="R15" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="T15" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
         <v>328</v>
@@ -1691,25 +1691,25 @@
         <v>866</v>
       </c>
       <c r="N16" t="n">
-        <v>2386</v>
+        <v>2118</v>
       </c>
       <c r="O16" t="n">
-        <v>2050</v>
+        <v>1798</v>
       </c>
       <c r="P16" t="n">
-        <v>1929</v>
+        <v>1682</v>
       </c>
       <c r="Q16" t="n">
-        <v>1562</v>
+        <v>1328</v>
       </c>
       <c r="R16" t="n">
-        <v>1238</v>
+        <v>1031</v>
       </c>
       <c r="S16" t="n">
-        <v>647</v>
+        <v>498</v>
       </c>
       <c r="T16" t="n">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="U16" t="n">
         <v>4037</v>
@@ -1770,25 +1770,25 @@
         <v>125</v>
       </c>
       <c r="N17" t="n">
-        <v>1002</v>
+        <v>971</v>
       </c>
       <c r="O17" t="n">
-        <v>859</v>
+        <v>830</v>
       </c>
       <c r="P17" t="n">
-        <v>801</v>
+        <v>773</v>
       </c>
       <c r="Q17" t="n">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="R17" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="S17" t="n">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="T17" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="U17" t="n">
         <v>1836</v>
@@ -1849,25 +1849,25 @@
         <v>2980</v>
       </c>
       <c r="N18" t="n">
-        <v>8137</v>
+        <v>7157</v>
       </c>
       <c r="O18" t="n">
-        <v>7303</v>
+        <v>6349</v>
       </c>
       <c r="P18" t="n">
-        <v>6965</v>
+        <v>6020</v>
       </c>
       <c r="Q18" t="n">
-        <v>5855</v>
+        <v>4968</v>
       </c>
       <c r="R18" t="n">
-        <v>4760</v>
+        <v>3946</v>
       </c>
       <c r="S18" t="n">
-        <v>2809</v>
+        <v>2156</v>
       </c>
       <c r="T18" t="n">
-        <v>1212</v>
+        <v>772</v>
       </c>
       <c r="U18" t="n">
         <v>12006</v>
@@ -1928,25 +1928,25 @@
         <v>452</v>
       </c>
       <c r="N19" t="n">
-        <v>2474</v>
+        <v>2310</v>
       </c>
       <c r="O19" t="n">
-        <v>2177</v>
+        <v>2021</v>
       </c>
       <c r="P19" t="n">
-        <v>2084</v>
+        <v>1930</v>
       </c>
       <c r="Q19" t="n">
-        <v>1707</v>
+        <v>1569</v>
       </c>
       <c r="R19" t="n">
-        <v>1392</v>
+        <v>1271</v>
       </c>
       <c r="S19" t="n">
-        <v>804</v>
+        <v>711</v>
       </c>
       <c r="T19" t="n">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="U19" t="n">
         <v>3515</v>
@@ -2165,25 +2165,25 @@
         <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>24</v>
@@ -2244,25 +2244,25 @@
         <v>39</v>
       </c>
       <c r="N23" t="n">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="O23" t="n">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="P23" t="n">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="Q23" t="n">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="R23" t="n">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="S23" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="T23" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="U23" t="n">
         <v>692</v>
@@ -2323,22 +2323,22 @@
         <v>32</v>
       </c>
       <c r="N24" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="O24" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P24" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Q24" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="R24" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="S24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T24" t="n">
         <v>12</v>
@@ -2402,22 +2402,22 @@
         <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O25" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="P25" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="Q25" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="R25" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="S25" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="T25" t="n">
         <v>13</v>
@@ -2876,25 +2876,25 @@
         <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
         <v>26</v>
@@ -3034,25 +3034,25 @@
         <v>258</v>
       </c>
       <c r="N33" t="n">
-        <v>1033</v>
+        <v>942</v>
       </c>
       <c r="O33" t="n">
-        <v>1023</v>
+        <v>932</v>
       </c>
       <c r="P33" t="n">
-        <v>1020</v>
+        <v>929</v>
       </c>
       <c r="Q33" t="n">
-        <v>792</v>
+        <v>705</v>
       </c>
       <c r="R33" t="n">
-        <v>683</v>
+        <v>598</v>
       </c>
       <c r="S33" t="n">
-        <v>362</v>
+        <v>285</v>
       </c>
       <c r="T33" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="U33" t="n">
         <v>3624</v>
@@ -3113,25 +3113,25 @@
         <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="O34" t="n">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="P34" t="n">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="Q34" t="n">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="R34" t="n">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="S34" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T34" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="U34" t="n">
         <v>495</v>
@@ -3192,25 +3192,25 @@
         <v>11</v>
       </c>
       <c r="N35" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P35" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
         <v>56</v>
@@ -3824,19 +3824,19 @@
         <v>15</v>
       </c>
       <c r="N43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -3982,22 +3982,22 @@
         <v>3385</v>
       </c>
       <c r="N45" t="n">
-        <v>3792</v>
+        <v>3610</v>
       </c>
       <c r="O45" t="n">
-        <v>2245</v>
+        <v>2126</v>
       </c>
       <c r="P45" t="n">
-        <v>1773</v>
+        <v>1676</v>
       </c>
       <c r="Q45" t="n">
-        <v>916</v>
+        <v>848</v>
       </c>
       <c r="R45" t="n">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="S45" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="T45" t="n">
         <v>2</v>
@@ -4140,22 +4140,22 @@
         <v>716</v>
       </c>
       <c r="N47" t="n">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="O47" t="n">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="P47" t="n">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="Q47" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="R47" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -4219,19 +4219,19 @@
         <v>9</v>
       </c>
       <c r="N48" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O48" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P48" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q48" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="R48" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S48" t="n">
         <v>55</v>
@@ -4377,10 +4377,10 @@
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -4456,19 +4456,19 @@
         <v>94</v>
       </c>
       <c r="N51" t="n">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="O51" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P51" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>3262</v>
       </c>
       <c r="N52" t="n">
-        <v>4510</v>
+        <v>4374</v>
       </c>
       <c r="O52" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
       <c r="P52" t="n">
-        <v>1501</v>
+        <v>1438</v>
       </c>
       <c r="Q52" t="n">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="R52" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="S52" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="T52" t="n">
         <v>2</v>
@@ -4614,19 +4614,19 @@
         <v>1186</v>
       </c>
       <c r="N53" t="n">
-        <v>1788</v>
+        <v>1739</v>
       </c>
       <c r="O53" t="n">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="P53" t="n">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="Q53" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="R53" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -4693,19 +4693,19 @@
         <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O54" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P54" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="R54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -5088,22 +5088,22 @@
         <v>115</v>
       </c>
       <c r="N59" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="O59" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P59" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q59" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R59" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S59" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T59" t="n">
         <v>16</v>
@@ -5404,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O63" t="n">
         <v>9</v>
@@ -5562,22 +5562,22 @@
         <v>33</v>
       </c>
       <c r="N65" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="O65" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P65" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q65" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R65" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T65" t="n">
         <v>6</v>
@@ -5641,22 +5641,22 @@
         <v>9</v>
       </c>
       <c r="N66" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="O66" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P66" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q66" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R66" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S66" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T66" t="n">
         <v>41</v>
@@ -5720,22 +5720,22 @@
         <v>16</v>
       </c>
       <c r="N67" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O67" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="P67" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q67" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R67" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="S67" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T67" t="n">
         <v>9</v>
@@ -5799,22 +5799,22 @@
         <v>11</v>
       </c>
       <c r="N68" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="O68" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="P68" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q68" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R68" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="S68" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T68" t="n">
         <v>15</v>
@@ -5878,10 +5878,10 @@
         <v>251</v>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
         <v>7</v>
@@ -6115,25 +6115,25 @@
         <v>56</v>
       </c>
       <c r="N72" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="O72" t="n">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="P72" t="n">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="Q72" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="R72" t="n">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="S72" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="T72" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="U72" t="n">
         <v>1607</v>
@@ -6668,19 +6668,19 @@
         <v>2</v>
       </c>
       <c r="N79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -6747,16 +6747,16 @@
         <v>83</v>
       </c>
       <c r="N80" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O80" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P80" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q80" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R80" t="n">
         <v>206</v>
@@ -6826,25 +6826,25 @@
         <v>16</v>
       </c>
       <c r="N81" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O81" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P81" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q81" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R81" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U81" t="n">
         <v>273</v>
@@ -7300,25 +7300,25 @@
         <v>322</v>
       </c>
       <c r="N87" t="n">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="O87" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="P87" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Q87" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="R87" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S87" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U87" t="n">
         <v>1122</v>
@@ -8011,22 +8011,22 @@
         <v>30</v>
       </c>
       <c r="N96" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O96" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P96" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q96" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R96" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S96" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T96" t="n">
         <v>1</v>
@@ -8090,25 +8090,25 @@
         <v>539</v>
       </c>
       <c r="N97" t="n">
-        <v>4673</v>
+        <v>4602</v>
       </c>
       <c r="O97" t="n">
-        <v>2846</v>
+        <v>2788</v>
       </c>
       <c r="P97" t="n">
-        <v>2355</v>
+        <v>2300</v>
       </c>
       <c r="Q97" t="n">
-        <v>1237</v>
+        <v>1199</v>
       </c>
       <c r="R97" t="n">
-        <v>683</v>
+        <v>654</v>
       </c>
       <c r="S97" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="T97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U97" t="n">
         <v>28525</v>
@@ -8169,19 +8169,19 @@
         <v>76</v>
       </c>
       <c r="N98" t="n">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="O98" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="P98" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q98" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R98" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S98" t="n">
         <v>14</v>
@@ -8327,19 +8327,19 @@
         <v>34</v>
       </c>
       <c r="N100" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="O100" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="P100" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q100" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="R100" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S100" t="n">
         <v>34</v>
@@ -8406,19 +8406,19 @@
         <v>123</v>
       </c>
       <c r="N101" t="n">
-        <v>2027</v>
+        <v>2012</v>
       </c>
       <c r="O101" t="n">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="P101" t="n">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="Q101" t="n">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="R101" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="S101" t="n">
         <v>26</v>
@@ -8643,7 +8643,7 @@
         <v>4</v>
       </c>
       <c r="N104" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O104" t="n">
         <v>14</v>
@@ -8722,13 +8722,13 @@
         <v>32</v>
       </c>
       <c r="N105" t="n">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O105" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P105" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q105" t="n">
         <v>80</v>
@@ -8880,25 +8880,25 @@
         <v>202</v>
       </c>
       <c r="N107" t="n">
-        <v>2634</v>
+        <v>2613</v>
       </c>
       <c r="O107" t="n">
-        <v>1431</v>
+        <v>1413</v>
       </c>
       <c r="P107" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="Q107" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="R107" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="S107" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U107" t="n">
         <v>26113</v>
@@ -8959,19 +8959,19 @@
         <v>81</v>
       </c>
       <c r="N108" t="n">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="O108" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P108" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Q108" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R108" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S108" t="n">
         <v>17</v>
@@ -9433,25 +9433,25 @@
         <v>39</v>
       </c>
       <c r="N114" t="n">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="O114" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="P114" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q114" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="R114" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="S114" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="T114" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U114" t="n">
         <v>1851</v>
@@ -9591,16 +9591,16 @@
         <v>8</v>
       </c>
       <c r="N116" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O116" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P116" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R116" t="n">
         <v>19</v>
@@ -9749,19 +9749,19 @@
         <v>4</v>
       </c>
       <c r="N118" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O118" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P118" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q118" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R118" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S118" t="n">
         <v>40</v>
@@ -10065,25 +10065,25 @@
         <v>169</v>
       </c>
       <c r="N122" t="n">
-        <v>3508</v>
+        <v>3441</v>
       </c>
       <c r="O122" t="n">
-        <v>2185</v>
+        <v>2122</v>
       </c>
       <c r="P122" t="n">
-        <v>2182</v>
+        <v>2119</v>
       </c>
       <c r="Q122" t="n">
-        <v>1606</v>
+        <v>1546</v>
       </c>
       <c r="R122" t="n">
-        <v>1238</v>
+        <v>1180</v>
       </c>
       <c r="S122" t="n">
-        <v>660</v>
+        <v>611</v>
       </c>
       <c r="T122" t="n">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="U122" t="n">
         <v>12173</v>
@@ -10144,25 +10144,25 @@
         <v>32</v>
       </c>
       <c r="N123" t="n">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="O123" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P123" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q123" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R123" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S123" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T123" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U123" t="n">
         <v>836</v>
@@ -11092,19 +11092,19 @@
         <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O135" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P135" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q135" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S135" t="n">
         <v>8</v>
@@ -11329,25 +11329,25 @@
         <v>13</v>
       </c>
       <c r="N138" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O138" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P138" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q138" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R138" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S138" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T138" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U138" t="n">
         <v>555</v>
@@ -11487,25 +11487,25 @@
         <v>169</v>
       </c>
       <c r="N140" t="n">
-        <v>3438</v>
+        <v>3421</v>
       </c>
       <c r="O140" t="n">
-        <v>2834</v>
+        <v>2817</v>
       </c>
       <c r="P140" t="n">
-        <v>2614</v>
+        <v>2597</v>
       </c>
       <c r="Q140" t="n">
-        <v>1912</v>
+        <v>1896</v>
       </c>
       <c r="R140" t="n">
-        <v>1431</v>
+        <v>1415</v>
       </c>
       <c r="S140" t="n">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="T140" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="U140" t="n">
         <v>6660</v>
@@ -11566,25 +11566,25 @@
         <v>125</v>
       </c>
       <c r="N141" t="n">
-        <v>1509</v>
+        <v>1497</v>
       </c>
       <c r="O141" t="n">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="P141" t="n">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="Q141" t="n">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="R141" t="n">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="S141" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="T141" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="U141" t="n">
         <v>2956</v>
@@ -11961,22 +11961,22 @@
         <v>536</v>
       </c>
       <c r="N146" t="n">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="O146" t="n">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="P146" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="Q146" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="R146" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="S146" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T146" t="n">
         <v>6</v>
@@ -12040,16 +12040,16 @@
         <v>3</v>
       </c>
       <c r="N147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R147" t="n">
         <v>1</v>
@@ -12356,25 +12356,25 @@
         <v>8501</v>
       </c>
       <c r="N151" t="n">
-        <v>40618</v>
+        <v>40115</v>
       </c>
       <c r="O151" t="n">
-        <v>23528</v>
+        <v>23139</v>
       </c>
       <c r="P151" t="n">
-        <v>18835</v>
+        <v>18479</v>
       </c>
       <c r="Q151" t="n">
-        <v>9907</v>
+        <v>9644</v>
       </c>
       <c r="R151" t="n">
-        <v>5933</v>
+        <v>5731</v>
       </c>
       <c r="S151" t="n">
-        <v>2082</v>
+        <v>1988</v>
       </c>
       <c r="T151" t="n">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="U151" t="n">
         <v>211615</v>
@@ -12435,22 +12435,22 @@
         <v>369</v>
       </c>
       <c r="N152" t="n">
-        <v>1221</v>
+        <v>1204</v>
       </c>
       <c r="O152" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="P152" t="n">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="Q152" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="R152" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="S152" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T152" t="n">
         <v>3</v>
@@ -12830,16 +12830,16 @@
         <v>20</v>
       </c>
       <c r="N157" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O157" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P157" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q157" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R157" t="n">
         <v>21</v>
@@ -13857,22 +13857,22 @@
         <v>4</v>
       </c>
       <c r="N170" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T170" t="n">
         <v>0</v>
@@ -13936,25 +13936,25 @@
         <v>1</v>
       </c>
       <c r="N171" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O171" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P171" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q171" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R171" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U171" t="n">
         <v>34</v>
@@ -15110,19 +15110,19 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P6" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q6" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R6" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T6" t="n">
         <v>40</v>
@@ -15530,25 +15530,25 @@
         <v>39</v>
       </c>
       <c r="O11" t="n">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="P11" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q11" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="R11" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="S11" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="T11" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="U11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="V11" t="n">
         <v>1851</v>
@@ -15698,16 +15698,16 @@
         <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S13" t="n">
         <v>19</v>
@@ -15866,25 +15866,25 @@
         <v>169</v>
       </c>
       <c r="O15" t="n">
-        <v>3508</v>
+        <v>3441</v>
       </c>
       <c r="P15" t="n">
-        <v>2185</v>
+        <v>2122</v>
       </c>
       <c r="Q15" t="n">
-        <v>2182</v>
+        <v>2119</v>
       </c>
       <c r="R15" t="n">
-        <v>1606</v>
+        <v>1546</v>
       </c>
       <c r="S15" t="n">
-        <v>1238</v>
+        <v>1180</v>
       </c>
       <c r="T15" t="n">
-        <v>660</v>
+        <v>611</v>
       </c>
       <c r="U15" t="n">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="V15" t="n">
         <v>12173</v>
@@ -15950,25 +15950,25 @@
         <v>32</v>
       </c>
       <c r="O16" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="P16" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="Q16" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="R16" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S16" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V16" t="n">
         <v>789</v>
@@ -16328,25 +16328,25 @@
         <v>26</v>
       </c>
       <c r="O2" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="P2" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="R2" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="S2" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="T2" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V2" t="n">
         <v>330</v>
@@ -16496,22 +16496,22 @@
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
         <v>4</v>
@@ -16664,19 +16664,19 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
         <v>4</v>
@@ -16748,25 +16748,25 @@
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V7" t="n">
         <v>62</v>
@@ -16832,25 +16832,25 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
         <v>62</v>
@@ -16916,25 +16916,25 @@
         <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>3</v>
@@ -17000,25 +17000,25 @@
         <v>866</v>
       </c>
       <c r="O10" t="n">
-        <v>2372</v>
+        <v>2104</v>
       </c>
       <c r="P10" t="n">
-        <v>2038</v>
+        <v>1786</v>
       </c>
       <c r="Q10" t="n">
-        <v>1919</v>
+        <v>1672</v>
       </c>
       <c r="R10" t="n">
-        <v>1553</v>
+        <v>1319</v>
       </c>
       <c r="S10" t="n">
-        <v>1232</v>
+        <v>1025</v>
       </c>
       <c r="T10" t="n">
-        <v>646</v>
+        <v>497</v>
       </c>
       <c r="U10" t="n">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="V10" t="n">
         <v>4014</v>
@@ -17084,25 +17084,25 @@
         <v>48</v>
       </c>
       <c r="O11" t="n">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="P11" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="Q11" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="R11" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="S11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="T11" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V11" t="n">
         <v>491</v>
@@ -17168,25 +17168,25 @@
         <v>2980</v>
       </c>
       <c r="O12" t="n">
-        <v>8137</v>
+        <v>7157</v>
       </c>
       <c r="P12" t="n">
-        <v>7303</v>
+        <v>6349</v>
       </c>
       <c r="Q12" t="n">
-        <v>6965</v>
+        <v>6020</v>
       </c>
       <c r="R12" t="n">
-        <v>5855</v>
+        <v>4968</v>
       </c>
       <c r="S12" t="n">
-        <v>4760</v>
+        <v>3946</v>
       </c>
       <c r="T12" t="n">
-        <v>2809</v>
+        <v>2156</v>
       </c>
       <c r="U12" t="n">
-        <v>1212</v>
+        <v>772</v>
       </c>
       <c r="V12" t="n">
         <v>12006</v>
@@ -17252,25 +17252,25 @@
         <v>17</v>
       </c>
       <c r="O13" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P13" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q13" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R13" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S13" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V13" t="n">
         <v>455</v>
@@ -17420,25 +17420,25 @@
         <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
         <v>39</v>
@@ -17588,25 +17588,25 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>30</v>
@@ -17756,25 +17756,25 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>28</v>
@@ -17840,22 +17840,22 @@
         <v>65</v>
       </c>
       <c r="O20" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P20" t="n">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="Q20" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="R20" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="S20" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="T20" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="U20" t="n">
         <v>17</v>
@@ -17924,25 +17924,25 @@
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="P21" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="Q21" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="R21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="S21" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="T21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="V21" t="n">
         <v>198</v>
@@ -18092,25 +18092,25 @@
         <v>26</v>
       </c>
       <c r="O23" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="P23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q23" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="R23" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="S23" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>179</v>
@@ -18176,25 +18176,25 @@
         <v>97</v>
       </c>
       <c r="O24" t="n">
-        <v>553</v>
+        <v>502</v>
       </c>
       <c r="P24" t="n">
-        <v>490</v>
+        <v>441</v>
       </c>
       <c r="Q24" t="n">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="R24" t="n">
-        <v>407</v>
+        <v>358</v>
       </c>
       <c r="S24" t="n">
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="T24" t="n">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="U24" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="V24" t="n">
         <v>750</v>
@@ -18260,22 +18260,22 @@
         <v>18</v>
       </c>
       <c r="O25" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="P25" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R25" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="S25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U25" t="n">
         <v>5</v>
@@ -18764,19 +18764,19 @@
         <v>14</v>
       </c>
       <c r="O31" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q31" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R31" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T31" t="n">
         <v>19</v>
@@ -18848,25 +18848,25 @@
         <v>16</v>
       </c>
       <c r="O32" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P32" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="Q32" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="R32" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="S32" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="T32" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="U32" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="V32" t="n">
         <v>408</v>
@@ -18932,25 +18932,25 @@
         <v>39</v>
       </c>
       <c r="O33" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="P33" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="Q33" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="R33" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="S33" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="T33" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="U33" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="V33" t="n">
         <v>99</v>
@@ -19100,25 +19100,25 @@
         <v>28</v>
       </c>
       <c r="O35" t="n">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="P35" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="Q35" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="R35" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="S35" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="T35" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="U35" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="V35" t="n">
         <v>373</v>
@@ -19184,25 +19184,25 @@
         <v>128</v>
       </c>
       <c r="O36" t="n">
-        <v>953</v>
+        <v>887</v>
       </c>
       <c r="P36" t="n">
-        <v>867</v>
+        <v>802</v>
       </c>
       <c r="Q36" t="n">
-        <v>836</v>
+        <v>772</v>
       </c>
       <c r="R36" t="n">
-        <v>704</v>
+        <v>646</v>
       </c>
       <c r="S36" t="n">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="T36" t="n">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="U36" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="V36" t="n">
         <v>1317</v>
@@ -19352,25 +19352,25 @@
         <v>140</v>
       </c>
       <c r="O38" t="n">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="P38" t="n">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="Q38" t="n">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="R38" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="S38" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="T38" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="U38" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V38" t="n">
         <v>411</v>
@@ -19436,25 +19436,25 @@
         <v>20</v>
       </c>
       <c r="O39" t="n">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="P39" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Q39" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="R39" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="S39" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="T39" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V39" t="n">
         <v>613</v>
@@ -19772,25 +19772,25 @@
         <v>5</v>
       </c>
       <c r="O43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>24</v>
@@ -19856,25 +19856,25 @@
         <v>39</v>
       </c>
       <c r="O44" t="n">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="P44" t="n">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="Q44" t="n">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="R44" t="n">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="S44" t="n">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="T44" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="U44" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="V44" t="n">
         <v>692</v>
@@ -19940,22 +19940,22 @@
         <v>25</v>
       </c>
       <c r="O45" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="P45" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Q45" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="R45" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="S45" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="T45" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="U45" t="n">
         <v>13</v>
@@ -20738,19 +20738,19 @@
         <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P3" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q3" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T3" t="n">
         <v>55</v>
@@ -20990,22 +20990,22 @@
         <v>3385</v>
       </c>
       <c r="O6" t="n">
-        <v>3792</v>
+        <v>3610</v>
       </c>
       <c r="P6" t="n">
-        <v>2245</v>
+        <v>2126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1773</v>
+        <v>1676</v>
       </c>
       <c r="R6" t="n">
-        <v>916</v>
+        <v>848</v>
       </c>
       <c r="S6" t="n">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="T6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -21074,22 +21074,22 @@
         <v>716</v>
       </c>
       <c r="O7" t="n">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="P7" t="n">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="Q7" t="n">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="R7" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="S7" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -21158,10 +21158,10 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -21242,19 +21242,19 @@
         <v>94</v>
       </c>
       <c r="O9" t="n">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="P9" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -21326,22 +21326,22 @@
         <v>3262</v>
       </c>
       <c r="O10" t="n">
-        <v>4510</v>
+        <v>4374</v>
       </c>
       <c r="P10" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1501</v>
+        <v>1438</v>
       </c>
       <c r="R10" t="n">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="S10" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="T10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -21410,19 +21410,19 @@
         <v>1186</v>
       </c>
       <c r="O11" t="n">
-        <v>1788</v>
+        <v>1739</v>
       </c>
       <c r="P11" t="n">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="Q11" t="n">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="R11" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="S11" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="T11" t="n">
         <v>10</v>
@@ -21494,19 +21494,19 @@
         <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
@@ -22208,22 +22208,22 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P7" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q7" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U7" t="n">
         <v>16</v>
@@ -24476,19 +24476,19 @@
         <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P34" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R34" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T34" t="n">
         <v>12</v>
@@ -24728,22 +24728,22 @@
         <v>115</v>
       </c>
       <c r="O37" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="P37" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q37" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R37" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S37" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U37" t="n">
         <v>16</v>
@@ -24896,7 +24896,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
         <v>9</v>
@@ -25064,22 +25064,22 @@
         <v>33</v>
       </c>
       <c r="O41" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="P41" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q41" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R41" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S41" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U41" t="n">
         <v>6</v>
@@ -25232,22 +25232,22 @@
         <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P43" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Q43" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="R43" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="S43" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="T43" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U43" t="n">
         <v>9</v>
@@ -25316,22 +25316,22 @@
         <v>11</v>
       </c>
       <c r="O44" t="n">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P44" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Q44" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="R44" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="S44" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="T44" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U44" t="n">
         <v>13</v>
@@ -26366,16 +26366,16 @@
         <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -26534,16 +26534,16 @@
         <v>22</v>
       </c>
       <c r="O7" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
         <v>45</v>
@@ -26702,25 +26702,25 @@
         <v>322</v>
       </c>
       <c r="O9" t="n">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="P9" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="Q9" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="R9" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="S9" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
         <v>1122</v>
@@ -27374,19 +27374,19 @@
         <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -27458,25 +27458,25 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>11</v>
@@ -28466,22 +28466,22 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -28676,19 +28676,19 @@
         <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="P2" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="Q2" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="R2" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="T2" t="n">
         <v>34</v>
@@ -28760,22 +28760,22 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -28844,7 +28844,7 @@
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
         <v>14</v>
@@ -28928,25 +28928,25 @@
         <v>539</v>
       </c>
       <c r="O5" t="n">
-        <v>4673</v>
+        <v>4602</v>
       </c>
       <c r="P5" t="n">
-        <v>2846</v>
+        <v>2788</v>
       </c>
       <c r="Q5" t="n">
-        <v>2355</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>1237</v>
+        <v>1199</v>
       </c>
       <c r="S5" t="n">
-        <v>683</v>
+        <v>654</v>
       </c>
       <c r="T5" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5" t="n">
         <v>28525</v>
@@ -29012,19 +29012,19 @@
         <v>76</v>
       </c>
       <c r="O6" t="n">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P6" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q6" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="R6" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T6" t="n">
         <v>14</v>
@@ -29180,19 +29180,19 @@
         <v>123</v>
       </c>
       <c r="O8" t="n">
-        <v>2027</v>
+        <v>2012</v>
       </c>
       <c r="P8" t="n">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="Q8" t="n">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="R8" t="n">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="S8" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="T8" t="n">
         <v>26</v>
@@ -29432,13 +29432,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P11" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R11" t="n">
         <v>80</v>
@@ -29600,25 +29600,25 @@
         <v>202</v>
       </c>
       <c r="O13" t="n">
-        <v>2634</v>
+        <v>2613</v>
       </c>
       <c r="P13" t="n">
-        <v>1431</v>
+        <v>1413</v>
       </c>
       <c r="Q13" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="R13" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="S13" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="T13" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
         <v>26113</v>
@@ -29684,19 +29684,19 @@
         <v>81</v>
       </c>
       <c r="O14" t="n">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="P14" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Q14" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="R14" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T14" t="n">
         <v>17</v>
@@ -31658,19 +31658,19 @@
         <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
         <v>8</v>
@@ -31910,25 +31910,25 @@
         <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P25" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q25" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R25" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S25" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T25" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V25" t="n">
         <v>555</v>
@@ -32078,25 +32078,25 @@
         <v>169</v>
       </c>
       <c r="O27" t="n">
-        <v>3438</v>
+        <v>3421</v>
       </c>
       <c r="P27" t="n">
-        <v>2834</v>
+        <v>2817</v>
       </c>
       <c r="Q27" t="n">
-        <v>2614</v>
+        <v>2597</v>
       </c>
       <c r="R27" t="n">
-        <v>1912</v>
+        <v>1896</v>
       </c>
       <c r="S27" t="n">
-        <v>1431</v>
+        <v>1415</v>
       </c>
       <c r="T27" t="n">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="U27" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="V27" t="n">
         <v>6660</v>
@@ -32162,25 +32162,25 @@
         <v>125</v>
       </c>
       <c r="O28" t="n">
-        <v>1509</v>
+        <v>1497</v>
       </c>
       <c r="P28" t="n">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="Q28" t="n">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="R28" t="n">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="S28" t="n">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="T28" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="U28" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="V28" t="n">
         <v>2956</v>
@@ -32414,22 +32414,22 @@
         <v>536</v>
       </c>
       <c r="O31" t="n">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="P31" t="n">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="Q31" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="R31" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="S31" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="T31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U31" t="n">
         <v>6</v>
@@ -32498,16 +32498,16 @@
         <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -32666,25 +32666,25 @@
         <v>8501</v>
       </c>
       <c r="O34" t="n">
-        <v>40618</v>
+        <v>40115</v>
       </c>
       <c r="P34" t="n">
-        <v>23528</v>
+        <v>23139</v>
       </c>
       <c r="Q34" t="n">
-        <v>18835</v>
+        <v>18479</v>
       </c>
       <c r="R34" t="n">
-        <v>9907</v>
+        <v>9644</v>
       </c>
       <c r="S34" t="n">
-        <v>5933</v>
+        <v>5731</v>
       </c>
       <c r="T34" t="n">
-        <v>2082</v>
+        <v>1988</v>
       </c>
       <c r="U34" t="n">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="V34" t="n">
         <v>211615</v>
@@ -32750,22 +32750,22 @@
         <v>369</v>
       </c>
       <c r="O35" t="n">
-        <v>1221</v>
+        <v>1204</v>
       </c>
       <c r="P35" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="Q35" t="n">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="R35" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="S35" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="T35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U35" t="n">
         <v>3</v>

--- a/summary_stats/chuuchuu_summary_2025_07.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_07.xlsx
@@ -14327,16 +14327,16 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O176" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P176" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q176" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R176" t="n">
         <v>32</v>
